--- a/kimariji_results2.xlsx
+++ b/kimariji_results2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="48" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="96" uniqueCount="12">
   <si>
     <t>FudaName</t>
   </si>
@@ -121,7 +121,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="0">
-        <v>0.60999999999999999</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="3">
@@ -132,7 +132,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="0">
-        <v>0.60999999999999999</v>
+        <v>0.64000000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -143,7 +143,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="0">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="5">
@@ -154,7 +154,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="0">
-        <v>0.56000000000000005</v>
+        <v>0.65000000000000002</v>
       </c>
     </row>
     <row r="6">
@@ -165,7 +165,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="0">
-        <v>0.60999999999999999</v>
+        <v>0.58000000000000007</v>
       </c>
     </row>
     <row r="7">
@@ -176,7 +176,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="0">
-        <v>0.53000000000000003</v>
+        <v>0.57000000000000006</v>
       </c>
     </row>
     <row r="8">
@@ -187,7 +187,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="0">
-        <v>0.52000000000000002</v>
+        <v>0.44000000000000006</v>
       </c>
     </row>
     <row r="9">
@@ -198,7 +198,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="0">
-        <v>0.59000000000000008</v>
+        <v>0.54000000000000004</v>
       </c>
     </row>
     <row r="10">
@@ -209,7 +209,7 @@
         <v>4</v>
       </c>
       <c r="C10" s="0">
-        <v>0.58000000000000007</v>
+        <v>0.57000000000000006</v>
       </c>
     </row>
     <row r="11">
@@ -220,7 +220,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="0">
-        <v>0.53000000000000003</v>
+        <v>0.46999999999999997</v>
       </c>
     </row>
     <row r="12">
@@ -231,7 +231,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="0">
-        <v>0.39000000000000001</v>
+        <v>0.35999999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -242,7 +242,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="0">
-        <v>0.39000000000000001</v>
+        <v>0.43000000000000005</v>
       </c>
     </row>
     <row r="14">
@@ -253,7 +253,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="0">
-        <v>0.42000000000000004</v>
+        <v>0.45999999999999996</v>
       </c>
     </row>
     <row r="15">
@@ -264,7 +264,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="0">
-        <v>0.40000000000000002</v>
+        <v>0.42000000000000004</v>
       </c>
     </row>
     <row r="16">
@@ -275,7 +275,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="0">
-        <v>0.40000000000000002</v>
+        <v>0.57000000000000006</v>
       </c>
     </row>
     <row r="17">
@@ -286,7 +286,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="0">
-        <v>0.42000000000000004</v>
+        <v>0.45999999999999996</v>
       </c>
     </row>
     <row r="18">
@@ -297,7 +297,7 @@
         <v>2</v>
       </c>
       <c r="C18" s="0">
-        <v>0.43000000000000005</v>
+        <v>0.47999999999999998</v>
       </c>
     </row>
     <row r="19">
@@ -308,7 +308,7 @@
         <v>3</v>
       </c>
       <c r="C19" s="0">
-        <v>0.45999999999999996</v>
+        <v>0.47999999999999998</v>
       </c>
     </row>
     <row r="20">
@@ -319,7 +319,7 @@
         <v>4</v>
       </c>
       <c r="C20" s="0">
-        <v>0.29000000000000004</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
@@ -330,7 +330,7 @@
         <v>5</v>
       </c>
       <c r="C21" s="0">
-        <v>0.48999999999999999</v>
+        <v>0.47999999999999998</v>
       </c>
     </row>
     <row r="22">
@@ -341,7 +341,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="0">
-        <v>0.44999999999999996</v>
+        <v>0.48999999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -352,7 +352,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="0">
-        <v>0.44000000000000006</v>
+        <v>0.45999999999999996</v>
       </c>
     </row>
     <row r="24">
@@ -363,7 +363,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="0">
-        <v>0.44000000000000006</v>
+        <v>0.48999999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -374,7 +374,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="0">
-        <v>0.45999999999999996</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="26">
@@ -385,7 +385,7 @@
         <v>5</v>
       </c>
       <c r="C26" s="0">
-        <v>0.46999999999999997</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="27">
@@ -396,7 +396,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="0">
-        <v>0.56000000000000005</v>
+        <v>0.53000000000000003</v>
       </c>
     </row>
     <row r="28">
@@ -407,7 +407,7 @@
         <v>2</v>
       </c>
       <c r="C28" s="0">
-        <v>0.58000000000000007</v>
+        <v>0.57000000000000006</v>
       </c>
     </row>
     <row r="29">
@@ -418,7 +418,7 @@
         <v>3</v>
       </c>
       <c r="C29" s="0">
-        <v>0.60000000000000009</v>
+        <v>0.59000000000000008</v>
       </c>
     </row>
     <row r="30">
@@ -429,7 +429,7 @@
         <v>4</v>
       </c>
       <c r="C30" s="0">
-        <v>0.59000000000000008</v>
+        <v>0.58000000000000007</v>
       </c>
     </row>
     <row r="31">
@@ -440,7 +440,7 @@
         <v>5</v>
       </c>
       <c r="C31" s="0">
-        <v>0.59000000000000008</v>
+        <v>0.60000000000000009</v>
       </c>
     </row>
     <row r="32">
@@ -451,7 +451,7 @@
         <v>1</v>
       </c>
       <c r="C32" s="0">
-        <v>0.58000000000000007</v>
+        <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="33">
@@ -462,7 +462,7 @@
         <v>2</v>
       </c>
       <c r="C33" s="0">
-        <v>0.58000000000000007</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="34">
@@ -473,7 +473,7 @@
         <v>3</v>
       </c>
       <c r="C34" s="0">
-        <v>0.59000000000000008</v>
+        <v>0.60999999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -484,7 +484,7 @@
         <v>4</v>
       </c>
       <c r="C35" s="0">
-        <v>0.56000000000000005</v>
+        <v>0.58000000000000007</v>
       </c>
     </row>
     <row r="36">
@@ -495,7 +495,7 @@
         <v>5</v>
       </c>
       <c r="C36" s="0">
-        <v>0.58000000000000007</v>
+        <v>0.60000000000000009</v>
       </c>
     </row>
     <row r="37">
@@ -506,7 +506,7 @@
         <v>1</v>
       </c>
       <c r="C37" s="0">
-        <v>0.48999999999999999</v>
+        <v>0.52000000000000002</v>
       </c>
     </row>
     <row r="38">
@@ -517,7 +517,7 @@
         <v>2</v>
       </c>
       <c r="C38" s="0">
-        <v>0.51000000000000001</v>
+        <v>0.44999999999999996</v>
       </c>
     </row>
     <row r="39">
@@ -528,7 +528,7 @@
         <v>3</v>
       </c>
       <c r="C39" s="0">
-        <v>0.51000000000000001</v>
+        <v>0.44000000000000006</v>
       </c>
     </row>
     <row r="40">
@@ -539,7 +539,7 @@
         <v>4</v>
       </c>
       <c r="C40" s="0">
-        <v>0.46999999999999997</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="41">
@@ -550,7 +550,7 @@
         <v>5</v>
       </c>
       <c r="C41" s="0">
-        <v>0.51000000000000001</v>
+        <v>0.41000000000000003</v>
       </c>
     </row>
     <row r="42">
@@ -561,7 +561,7 @@
         <v>1</v>
       </c>
       <c r="C42" s="0">
-        <v>0.5</v>
+        <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="43">
@@ -572,7 +572,7 @@
         <v>2</v>
       </c>
       <c r="C43" s="0">
-        <v>0.51000000000000001</v>
+        <v>0.55000000000000005</v>
       </c>
     </row>
     <row r="44">
@@ -583,7 +583,7 @@
         <v>3</v>
       </c>
       <c r="C44" s="0">
-        <v>0.54000000000000004</v>
+        <v>0.20999999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -605,7 +605,7 @@
         <v>5</v>
       </c>
       <c r="C46" s="0">
-        <v>0.60999999999999999</v>
+        <v>0.46999999999999997</v>
       </c>
     </row>
   </sheetData>
